--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-23).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-23).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 4.182,57</t>
-  </si>
-  <si>
-    <t>46.2</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>4.88</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.187,86</t>
+  </si>
+  <si>
+    <t>46.3</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>4.89</t>
   </si>
   <si>
     <t>18.7</t>
@@ -956,13 +956,13 @@
     <t>7.0</t>
   </si>
   <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>46.7%</t>
-  </si>
-  <si>
-    <t>18.7%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>46.1%</t>
+  </si>
+  <si>
+    <t>18.6%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -974,7 +974,7 @@
     <t>4.7%</t>
   </si>
   <si>
-    <t>1.4%</t>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -989,19 +989,19 @@
     <t>4.3%</t>
   </si>
   <si>
-    <t>1162.0</t>
-  </si>
-  <si>
-    <t>940.0</t>
-  </si>
-  <si>
-    <t>83.0</t>
+    <t>1198.0</t>
+  </si>
+  <si>
+    <t>971.0</t>
+  </si>
+  <si>
+    <t>85.0</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>238.0</t>
+    <t>244.0</t>
   </si>
   <si>
     <t>70.0</t>
@@ -1010,13 +1010,13 @@
     <t>16.0</t>
   </si>
   <si>
-    <t>356.0</t>
-  </si>
-  <si>
-    <t>153.0</t>
-  </si>
-  <si>
-    <t>216.0</t>
+    <t>371.0</t>
+  </si>
+  <si>
+    <t>156.0</t>
+  </si>
+  <si>
+    <t>226.0</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -3242,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3272,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>6863.7600000000002</v>
+      </c>
+      <c r="N13" s="6">
+        <v>75</v>
+      </c>
+      <c r="O13" s="6">
+        <v>55</v>
+      </c>
+      <c r="P13" s="7">
+        <v>6.1448202702702703</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>19.405454545454546</v>
+      </c>
+      <c r="R13" s="8">
+        <v>6.6303036363636361</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.30909090909090908</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -7609,7 +7667,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7639,35 +7697,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>2882.3099999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>36</v>
+      </c>
+      <c r="O42" s="6">
+        <v>24</v>
+      </c>
+      <c r="P42" s="7">
+        <v>4.3122558823529413</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>14.653470833333332</v>
+      </c>
+      <c r="R42" s="8">
+        <v>3.2717391304347827</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9057,7 +9173,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>51</v>
@@ -9087,35 +9203,93 @@
         <v>58</v>
       </c>
       <c r="L52" s="4"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="9"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="9"/>
-      <c r="W52" s="9"/>
-      <c r="X52" s="9"/>
-      <c r="Y52" s="9"/>
-      <c r="Z52" s="9"/>
-      <c r="AA52" s="9"/>
-      <c r="AB52" s="9"/>
-      <c r="AC52" s="9"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="6"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="6"/>
-      <c r="AL52" s="6"/>
-      <c r="AM52" s="6"/>
-      <c r="AN52" s="9"/>
-      <c r="AO52" s="6"/>
+      <c r="M52" s="5">
+        <v>4573.1000000000004</v>
+      </c>
+      <c r="N52" s="6">
+        <v>44</v>
+      </c>
+      <c r="O52" s="6">
+        <v>18</v>
+      </c>
+      <c r="P52" s="7">
+        <v>6.9405804347826088</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>16.341666666666665</v>
+      </c>
+      <c r="R52" s="8">
+        <v>2.8858999999999999</v>
+      </c>
+      <c r="S52" s="8">
+        <v>8</v>
+      </c>
+      <c r="T52" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U52" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V52" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="W52" s="9">
+        <v>0</v>
+      </c>
+      <c r="X52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AB52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP52" s="4">
         <v>58</v>
       </c>
@@ -9190,7 +9364,9 @@
       <c r="N53" s="6">
         <v>42</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>31</v>
+      </c>
       <c r="P53" s="7">
         <v>3.3841261904761901</v>
       </c>
@@ -9200,31 +9376,75 @@
       <c r="R53" s="8">
         <v>3.2526870967741934</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.64516129032258063</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -9891,7 +10111,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -9921,18 +10141,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>4574.1499999999996</v>
+      </c>
+      <c r="N58" s="6">
+        <v>56</v>
+      </c>
       <c r="O58" s="6">
         <v>41</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>2.974405357142857</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.039024390243902</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.2299999999999995</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.3902439024390244</v>
+      </c>
       <c r="U58" s="9">
         <v>0.073170731707317069</v>
       </c>
@@ -11695,7 +11927,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>51</v>
@@ -11725,18 +11957,30 @@
         <v>58</v>
       </c>
       <c r="L70" s="4"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6"/>
+      <c r="M70" s="5">
+        <v>3936.3499999999999</v>
+      </c>
+      <c r="N70" s="6">
+        <v>48</v>
+      </c>
       <c r="O70" s="6">
         <v>21</v>
       </c>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
+      <c r="P70" s="7">
+        <v>3.134313725490196</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>20.331747619047619</v>
+      </c>
+      <c r="R70" s="8">
+        <v>10.778335</v>
+      </c>
       <c r="S70" s="8">
         <v>7</v>
       </c>
-      <c r="T70" s="9"/>
+      <c r="T70" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="U70" s="9">
         <v>0.23809523809523808</v>
       </c>
@@ -12593,7 +12837,9 @@
       <c r="N76" s="6">
         <v>79</v>
       </c>
-      <c r="O76" s="6"/>
+      <c r="O76" s="6">
+        <v>45</v>
+      </c>
       <c r="P76" s="7">
         <v>2.9339426829268294</v>
       </c>
@@ -12603,31 +12849,75 @@
       <c r="R76" s="8">
         <v>7.7333325581395345</v>
       </c>
-      <c r="S76" s="8"/>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
       <c r="T76" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="U76" s="9">
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.088888888888888892</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -25106,7 +25396,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>51</v>
@@ -25136,10 +25426,16 @@
         <v>58</v>
       </c>
       <c r="L161" s="4"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="6"/>
+      <c r="M161" s="5">
+        <v>3240.5999999999999</v>
+      </c>
+      <c r="N161" s="6">
+        <v>41</v>
+      </c>
       <c r="O161" s="6"/>
-      <c r="P161" s="7"/>
+      <c r="P161" s="7">
+        <v>7.9070824999999996</v>
+      </c>
       <c r="Q161" s="8"/>
       <c r="R161" s="8"/>
       <c r="S161" s="8"/>
@@ -27846,7 +28142,9 @@
       <c r="N179" s="6">
         <v>56</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>23</v>
+      </c>
       <c r="P179" s="7">
         <v>3.8938277777777777</v>
       </c>
@@ -27856,31 +28154,75 @@
       <c r="R179" s="8">
         <v>3.2804347826086957</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.78260869565217395</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
